--- a/01_analyses_states/Assam/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Assam/results/SoIB_summaries.xlsx
@@ -512,7 +512,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -523,13 +523,13 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>14.3</v>
+        <v>12.5</v>
       </c>
       <c r="E3">
-        <v>17.5</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -537,16 +537,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>85.7</v>
+        <v>87.5</v>
       </c>
       <c r="E4">
-        <v>72.5</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -563,7 +563,7 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -580,7 +580,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -588,10 +588,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>102</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -599,10 +599,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="C8">
-        <v>416</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -697,7 +697,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -705,7 +705,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -713,7 +713,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -742,7 +742,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>558</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -750,10 +750,10 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -761,10 +761,10 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -807,16 +807,16 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2">
-        <v>61.3</v>
+        <v>61.7</v>
       </c>
       <c r="D2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -827,13 +827,13 @@
         <v>41</v>
       </c>
       <c r="C3">
-        <v>38.7</v>
+        <v>38.3</v>
       </c>
       <c r="D3">
         <v>17</v>
       </c>
       <c r="E3">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
     </row>
   </sheetData>
